--- a/سجل الايرادات والمصروفات (version 1).xlsb.xlsx
+++ b/سجل الايرادات والمصروفات (version 1).xlsb.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Henu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E13AEFB-7A81-4AA7-88EA-633D5F84D058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DCB9BB-DB92-40F9-A3F5-1B9D74E573F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{B3249B00-A14B-4484-9177-C0A03E3FFFA3}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="137">
   <si>
     <t>هوستل الأهرامات — سجل حركة صندوق المصروفات النثرية</t>
   </si>
@@ -306,9 +305,6 @@
     <t>افطار غرفتين يومي 13 و14 اغسطس</t>
   </si>
   <si>
-    <t xml:space="preserve">عهده مع منسي </t>
-  </si>
-  <si>
     <t xml:space="preserve">توصيل المفروشات </t>
   </si>
   <si>
@@ -400,6 +396,63 @@
   </si>
   <si>
     <t>مناديل ورول تواليت</t>
+  </si>
+  <si>
+    <t>فاتورة التليفونات الارضي</t>
+  </si>
+  <si>
+    <t>فاتورة الانترنت الارضي</t>
+  </si>
+  <si>
+    <t>هدايا للاطفال</t>
+  </si>
+  <si>
+    <t>لبن ومصفاة للمطبخ</t>
+  </si>
+  <si>
+    <t>كباب وكفتة</t>
+  </si>
+  <si>
+    <t>فاتورة ماكدوتالدز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فاتورة بيزا هت </t>
+  </si>
+  <si>
+    <t xml:space="preserve">سلفة من الراتب ل يوسف </t>
+  </si>
+  <si>
+    <t>سلفة من الراتب ل جومانة</t>
+  </si>
+  <si>
+    <t>ثلج</t>
+  </si>
+  <si>
+    <t>شاليموه</t>
+  </si>
+  <si>
+    <t>ايراد غرفة 406 3 ليالي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دفعة من حساب المفروشات </t>
+  </si>
+  <si>
+    <t xml:space="preserve">باقي 13230 دفعة اخيرة وتم استلام كل الطلبية اذن تسليم رقم بيان سعر رقم 4113 بتاريخ 22 اغسطس </t>
+  </si>
+  <si>
+    <t>عهدة الاستقبال</t>
+  </si>
+  <si>
+    <t>حسب الكشف المرفق</t>
+  </si>
+  <si>
+    <t>جركن زيت للمصعد 410 و 370 افطار الغرف 3 ايام و100 مسامير ومستلزمات تركيب الاسرة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فواتير مياه 4 شهور </t>
+  </si>
+  <si>
+    <t>فاتورة مكافحةالحشرات شهر اغسطس</t>
   </si>
 </sst>
 </file>
@@ -3284,7 +3337,7 @@
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="10" t="s">
-        <v>87</v>
+        <v>133</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5">
@@ -3300,7 +3353,9 @@
         <f t="shared" si="0"/>
         <v>مقبول</v>
       </c>
-      <c r="L8" s="5"/>
+      <c r="L8" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
     </row>
@@ -3314,7 +3369,7 @@
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5">
@@ -3344,7 +3399,7 @@
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5">
@@ -3361,7 +3416,7 @@
         <v>مقبول</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
@@ -3376,7 +3431,7 @@
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5">
@@ -3393,7 +3448,7 @@
         <v>مقبول</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
@@ -3408,7 +3463,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5">
@@ -3438,7 +3493,7 @@
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -3468,7 +3523,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -3498,17 +3553,17 @@
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5">
-        <v>390</v>
+        <v>270</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="5">
         <f t="shared" si="1"/>
-        <v>279146</v>
+        <v>279266</v>
       </c>
       <c r="K15" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3528,7 +3583,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -3538,7 +3593,7 @@
       <c r="I16" s="5"/>
       <c r="J16" s="5">
         <f t="shared" si="1"/>
-        <v>281146</v>
+        <v>281266</v>
       </c>
       <c r="K16" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3558,7 +3613,7 @@
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5">
@@ -3568,7 +3623,7 @@
       <c r="I17" s="5"/>
       <c r="J17" s="5">
         <f t="shared" si="1"/>
-        <v>61146</v>
+        <v>61266</v>
       </c>
       <c r="K17" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3588,7 +3643,7 @@
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5">
@@ -3598,7 +3653,7 @@
       <c r="I18" s="5"/>
       <c r="J18" s="5">
         <f t="shared" si="1"/>
-        <v>60146</v>
+        <v>60266</v>
       </c>
       <c r="K18" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3618,7 +3673,7 @@
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5">
@@ -3628,7 +3683,7 @@
       <c r="I19" s="5"/>
       <c r="J19" s="5">
         <f t="shared" si="1"/>
-        <v>59146</v>
+        <v>59266</v>
       </c>
       <c r="K19" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3647,7 +3702,7 @@
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5">
@@ -3657,7 +3712,7 @@
       <c r="I20" s="5"/>
       <c r="J20" s="5">
         <f t="shared" si="1"/>
-        <v>59046</v>
+        <v>59166</v>
       </c>
       <c r="K20" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3677,7 +3732,7 @@
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5">
@@ -3687,7 +3742,7 @@
       <c r="I21" s="5"/>
       <c r="J21" s="5">
         <f t="shared" si="1"/>
-        <v>58746</v>
+        <v>58866</v>
       </c>
       <c r="K21" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3707,7 +3762,7 @@
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5">
@@ -3717,7 +3772,7 @@
       <c r="I22" s="5"/>
       <c r="J22" s="5">
         <f t="shared" si="1"/>
-        <v>58246</v>
+        <v>58366</v>
       </c>
       <c r="K22" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3737,7 +3792,7 @@
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -3747,14 +3802,14 @@
       <c r="I23" s="5"/>
       <c r="J23" s="5">
         <f t="shared" si="1"/>
-        <v>78246</v>
+        <v>78366</v>
       </c>
       <c r="K23" s="5" t="str">
         <f t="shared" si="0"/>
         <v>مقبول</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
@@ -3769,7 +3824,7 @@
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5">
@@ -3779,7 +3834,7 @@
       <c r="I24" s="5"/>
       <c r="J24" s="5">
         <f t="shared" si="1"/>
-        <v>76346</v>
+        <v>76466</v>
       </c>
       <c r="K24" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3799,7 +3854,7 @@
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5">
@@ -3809,7 +3864,7 @@
       <c r="I25" s="5"/>
       <c r="J25" s="5">
         <f t="shared" si="1"/>
-        <v>76246</v>
+        <v>76366</v>
       </c>
       <c r="K25" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3829,7 +3884,7 @@
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5">
@@ -3839,7 +3894,7 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5">
         <f t="shared" si="1"/>
-        <v>75146</v>
+        <v>75266</v>
       </c>
       <c r="K26" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3859,7 +3914,7 @@
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5">
@@ -3869,7 +3924,7 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5">
         <f t="shared" si="1"/>
-        <v>65846</v>
+        <v>65966</v>
       </c>
       <c r="K27" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3889,7 +3944,7 @@
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5">
@@ -3899,14 +3954,14 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5">
         <f t="shared" si="1"/>
-        <v>65446</v>
+        <v>65566</v>
       </c>
       <c r="K28" s="5" t="str">
         <f t="shared" si="0"/>
         <v>مقبول</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
@@ -3921,7 +3976,7 @@
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5">
@@ -3931,7 +3986,7 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5">
         <f t="shared" si="1"/>
-        <v>64781</v>
+        <v>64901</v>
       </c>
       <c r="K29" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3951,7 +4006,7 @@
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5">
@@ -3961,7 +4016,7 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5">
         <f t="shared" si="1"/>
-        <v>63881</v>
+        <v>64001</v>
       </c>
       <c r="K30" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3981,7 +4036,7 @@
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5">
@@ -3991,7 +4046,7 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5">
         <f t="shared" si="1"/>
-        <v>63681</v>
+        <v>63801</v>
       </c>
       <c r="K31" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4011,7 +4066,7 @@
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -4021,14 +4076,14 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5">
         <f t="shared" si="1"/>
-        <v>72981</v>
+        <v>73101</v>
       </c>
       <c r="K32" s="5" t="str">
         <f t="shared" si="0"/>
         <v>مقبول</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
@@ -4043,7 +4098,7 @@
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5">
@@ -4053,7 +4108,7 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5">
         <f t="shared" si="1"/>
-        <v>72721</v>
+        <v>72841</v>
       </c>
       <c r="K33" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4073,7 +4128,7 @@
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5">
@@ -4083,7 +4138,7 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5">
         <f t="shared" si="1"/>
-        <v>72521</v>
+        <v>72641</v>
       </c>
       <c r="K34" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4104,7 +4159,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="6">
         <f>SUM(G4:G34)</f>
-        <v>287319</v>
+        <v>287199</v>
       </c>
       <c r="H35" s="6">
         <f>SUM(H4:H34)</f>
@@ -4126,7 +4181,7 @@
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="H38">
         <f>J34-H37</f>
-        <v>10691</v>
+        <v>10811</v>
       </c>
     </row>
   </sheetData>
@@ -4139,7 +4194,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39D1CF39-8DC9-42AF-B7E0-53DD3728516E}">
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.90625" bestFit="1" customWidth="1"/>
@@ -4251,7 +4306,7 @@
       <c r="F4" s="12"/>
       <c r="G4" s="12">
         <f>'1-B Petty Cash'!G35</f>
-        <v>287319</v>
+        <v>287199</v>
       </c>
       <c r="H4" s="12">
         <f>'1-B Petty Cash'!H35</f>
@@ -4260,7 +4315,7 @@
       <c r="I4" s="12"/>
       <c r="J4" s="12">
         <f>C4-G4+H4</f>
-        <v>72521</v>
+        <v>72641</v>
       </c>
       <c r="K4" s="12" t="str">
         <f t="shared" ref="K4:K34" si="0">IF(J4&lt;200,"تنبيه: اعد التعبئة","مقبول")</f>
@@ -4280,7 +4335,7 @@
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5">
@@ -4290,7 +4345,7 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5">
         <f t="shared" ref="J5:J34" si="1">J4-G5+H5</f>
-        <v>72206</v>
+        <v>72326</v>
       </c>
       <c r="K5" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4301,18 +4356,26 @@
       <c r="N5" s="5"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A6" s="5"/>
-      <c r="B6" s="9"/>
+      <c r="A6" s="5">
+        <v>94</v>
+      </c>
+      <c r="B6" s="9">
+        <v>46254</v>
+      </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
+      <c r="E6" s="5" t="s">
+        <v>118</v>
+      </c>
       <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
+      <c r="G6" s="5">
+        <v>145</v>
+      </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>72181</v>
       </c>
       <c r="K6" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4323,18 +4386,26 @@
       <c r="N6" s="5"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="5"/>
-      <c r="B7" s="9"/>
+      <c r="A7" s="5">
+        <v>95</v>
+      </c>
+      <c r="B7" s="9">
+        <v>46254</v>
+      </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="10"/>
+      <c r="E7" s="10" t="s">
+        <v>119</v>
+      </c>
       <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="G7" s="5">
+        <v>1900</v>
+      </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>70281</v>
       </c>
       <c r="K7" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4345,18 +4416,26 @@
       <c r="N7" s="5"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="5"/>
-      <c r="B8" s="9"/>
+      <c r="A8" s="5">
+        <v>96</v>
+      </c>
+      <c r="B8" s="9">
+        <v>46254</v>
+      </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
-      <c r="E8" s="10"/>
+      <c r="E8" s="10" t="s">
+        <v>120</v>
+      </c>
       <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
+      <c r="G8" s="5">
+        <v>190</v>
+      </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>70091</v>
       </c>
       <c r="K8" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4367,18 +4446,26 @@
       <c r="N8" s="5"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="5"/>
-      <c r="B9" s="9"/>
+      <c r="A9" s="5">
+        <v>97</v>
+      </c>
+      <c r="B9" s="9">
+        <v>46254</v>
+      </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
-      <c r="E9" s="10"/>
+      <c r="E9" s="10" t="s">
+        <v>121</v>
+      </c>
       <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="G9" s="5">
+        <v>145</v>
+      </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
       <c r="J9" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>69946</v>
       </c>
       <c r="K9" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4389,18 +4476,26 @@
       <c r="N9" s="5"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="5"/>
-      <c r="B10" s="9"/>
+      <c r="A10" s="5">
+        <v>98</v>
+      </c>
+      <c r="B10" s="9">
+        <v>46254</v>
+      </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
-      <c r="E10" s="10"/>
+      <c r="E10" s="10" t="s">
+        <v>122</v>
+      </c>
       <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="G10" s="5">
+        <v>2150</v>
+      </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>67796</v>
       </c>
       <c r="K10" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4411,18 +4506,26 @@
       <c r="N10" s="5"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="5"/>
-      <c r="B11" s="9"/>
+      <c r="A11" s="5">
+        <v>99</v>
+      </c>
+      <c r="B11" s="9">
+        <v>46255</v>
+      </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="10"/>
+      <c r="E11" s="10" t="s">
+        <v>123</v>
+      </c>
       <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="G11" s="5">
+        <v>2020</v>
+      </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
       <c r="J11" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>65776</v>
       </c>
       <c r="K11" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4433,18 +4536,26 @@
       <c r="N11" s="5"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="5"/>
-      <c r="B12" s="9"/>
+      <c r="A12" s="5">
+        <v>100</v>
+      </c>
+      <c r="B12" s="9">
+        <v>46255</v>
+      </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="10"/>
+      <c r="E12" s="10" t="s">
+        <v>124</v>
+      </c>
       <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="G12" s="5">
+        <v>970</v>
+      </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>64806</v>
       </c>
       <c r="K12" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4455,18 +4566,26 @@
       <c r="N12" s="5"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="5"/>
-      <c r="B13" s="9"/>
+      <c r="A13" s="5">
+        <v>101</v>
+      </c>
+      <c r="B13" s="9">
+        <v>46255</v>
+      </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
-      <c r="E13" s="10"/>
+      <c r="E13" s="10" t="s">
+        <v>125</v>
+      </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+      <c r="G13" s="5">
+        <v>200</v>
+      </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>64606</v>
       </c>
       <c r="K13" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4477,18 +4596,26 @@
       <c r="N13" s="5"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="5"/>
-      <c r="B14" s="9"/>
+      <c r="A14" s="5">
+        <v>102</v>
+      </c>
+      <c r="B14" s="9">
+        <v>46255</v>
+      </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
+      <c r="E14" s="5" t="s">
+        <v>126</v>
+      </c>
       <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="G14" s="5">
+        <v>50</v>
+      </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>64556</v>
       </c>
       <c r="K14" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4499,18 +4626,26 @@
       <c r="N14" s="5"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="5"/>
-      <c r="B15" s="9"/>
+      <c r="A15" s="5">
+        <v>103</v>
+      </c>
+      <c r="B15" s="9">
+        <v>46255</v>
+      </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
+      <c r="E15" s="5" t="s">
+        <v>127</v>
+      </c>
       <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="G15" s="5">
+        <v>100</v>
+      </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>64456</v>
       </c>
       <c r="K15" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4521,18 +4656,26 @@
       <c r="N15" s="5"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="5"/>
-      <c r="B16" s="9"/>
+      <c r="A16" s="5">
+        <v>104</v>
+      </c>
+      <c r="B16" s="9">
+        <v>46255</v>
+      </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
+      <c r="E16" s="5" t="s">
+        <v>128</v>
+      </c>
       <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
+      <c r="G16" s="5">
+        <v>50</v>
+      </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
       <c r="J16" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>64406</v>
       </c>
       <c r="K16" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4543,18 +4686,26 @@
       <c r="N16" s="5"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="5"/>
-      <c r="B17" s="9"/>
+      <c r="A17" s="5">
+        <v>105</v>
+      </c>
+      <c r="B17" s="9">
+        <v>46256</v>
+      </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
+      <c r="E17" s="5" t="s">
+        <v>129</v>
+      </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
+      <c r="H17" s="5">
+        <v>2100</v>
+      </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>66506</v>
       </c>
       <c r="K17" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4569,20 +4720,26 @@
       <c r="B18" s="9"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
+      <c r="E18" s="5" t="s">
+        <v>130</v>
+      </c>
       <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
+      <c r="G18" s="5">
+        <v>30000</v>
+      </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>36506</v>
       </c>
       <c r="K18" s="5" t="str">
         <f t="shared" si="0"/>
         <v>مقبول</v>
       </c>
-      <c r="L18" s="5"/>
+      <c r="L18" s="5" t="s">
+        <v>131</v>
+      </c>
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
     </row>
@@ -4591,14 +4748,18 @@
       <c r="B19" s="9"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
+      <c r="E19" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
+      <c r="G19" s="5">
+        <v>2000</v>
+      </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>34506</v>
       </c>
       <c r="K19" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4612,14 +4773,18 @@
       <c r="B20" s="9"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
+      <c r="E20" s="5" t="s">
+        <v>135</v>
+      </c>
       <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
+      <c r="G20" s="5">
+        <v>7250</v>
+      </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>27256</v>
       </c>
       <c r="K20" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4634,14 +4799,18 @@
       <c r="B21" s="9"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
+      <c r="E21" s="5" t="s">
+        <v>136</v>
+      </c>
       <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
+      <c r="G21" s="5">
+        <v>2500</v>
+      </c>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>24756</v>
       </c>
       <c r="K21" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4663,7 +4832,7 @@
       <c r="I22" s="5"/>
       <c r="J22" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>24756</v>
       </c>
       <c r="K22" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4685,7 +4854,7 @@
       <c r="I23" s="5"/>
       <c r="J23" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>24756</v>
       </c>
       <c r="K23" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4707,7 +4876,7 @@
       <c r="I24" s="5"/>
       <c r="J24" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>24756</v>
       </c>
       <c r="K24" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4729,7 +4898,7 @@
       <c r="I25" s="5"/>
       <c r="J25" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>24756</v>
       </c>
       <c r="K25" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4751,7 +4920,7 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>24756</v>
       </c>
       <c r="K26" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4773,7 +4942,7 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>24756</v>
       </c>
       <c r="K27" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4795,7 +4964,7 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>24756</v>
       </c>
       <c r="K28" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4817,7 +4986,7 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>24756</v>
       </c>
       <c r="K29" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4839,7 +5008,7 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>24756</v>
       </c>
       <c r="K30" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4861,7 +5030,7 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>24756</v>
       </c>
       <c r="K31" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4883,7 +5052,7 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>24756</v>
       </c>
       <c r="K32" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4905,7 +5074,7 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>24756</v>
       </c>
       <c r="K33" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4927,7 +5096,7 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5">
         <f t="shared" si="1"/>
-        <v>72206</v>
+        <v>24756</v>
       </c>
       <c r="K34" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4948,11 +5117,11 @@
       <c r="F35" s="6"/>
       <c r="G35" s="6">
         <f>SUM(G4:G34)</f>
-        <v>287634</v>
+        <v>337184</v>
       </c>
       <c r="H35" s="6">
         <f>SUM(H4:H34)</f>
-        <v>359840</v>
+        <v>361940</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
@@ -4960,6 +5129,24 @@
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="G37">
+        <f>25000+150+145</f>
+        <v>25295</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="G38">
+        <f>J34-G37</f>
+        <v>-539</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="G39">
+        <f>10914-G38</f>
+        <v>11453</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/سجل الايرادات والمصروفات (version 1).xlsb.xlsx
+++ b/سجل الايرادات والمصروفات (version 1).xlsb.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Henu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DCB9BB-DB92-40F9-A3F5-1B9D74E573F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FF8003-D992-4AD4-BA33-27E676F9D2F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{B3249B00-A14B-4484-9177-C0A03E3FFFA3}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="143">
   <si>
     <t>هوستل الأهرامات — سجل حركة صندوق المصروفات النثرية</t>
   </si>
@@ -453,6 +453,24 @@
   </si>
   <si>
     <t>فاتورة مكافحةالحشرات شهر اغسطس</t>
+  </si>
+  <si>
+    <t>سلفة استاذ خالد</t>
+  </si>
+  <si>
+    <t>مصاريف عمل سقالة لاستكمال الرسومات</t>
+  </si>
+  <si>
+    <t>غسيل ومكوة للمفروشات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مصروفات  من 22 الى 24 اغسطس حسب الكشف </t>
+  </si>
+  <si>
+    <t>سلفة من الراتب محمد المنسي</t>
+  </si>
+  <si>
+    <t>سلفة من الراتب مدحت</t>
   </si>
 </sst>
 </file>
@@ -4194,7 +4212,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39D1CF39-8DC9-42AF-B7E0-53DD3728516E}">
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.90625" bestFit="1" customWidth="1"/>
@@ -4716,8 +4734,12 @@
       <c r="N17" s="5"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="5"/>
-      <c r="B18" s="9"/>
+      <c r="A18" s="5">
+        <v>106</v>
+      </c>
+      <c r="B18" s="9">
+        <v>46257</v>
+      </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
@@ -4744,8 +4766,12 @@
       <c r="N18" s="5"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="5"/>
-      <c r="B19" s="9"/>
+      <c r="A19" s="5">
+        <v>107</v>
+      </c>
+      <c r="B19" s="9">
+        <v>46257</v>
+      </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
@@ -4769,8 +4795,12 @@
       <c r="N19" s="5"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="5"/>
-      <c r="B20" s="9"/>
+      <c r="A20" s="5">
+        <v>108</v>
+      </c>
+      <c r="B20" s="9">
+        <v>46257</v>
+      </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
@@ -4795,8 +4825,12 @@
       <c r="N20" s="5"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="5"/>
-      <c r="B21" s="9"/>
+      <c r="A21" s="5">
+        <v>109</v>
+      </c>
+      <c r="B21" s="9">
+        <v>46257</v>
+      </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
@@ -4821,18 +4855,26 @@
       <c r="N21" s="5"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="5"/>
-      <c r="B22" s="9"/>
+      <c r="A22" s="5">
+        <v>110</v>
+      </c>
+      <c r="B22" s="9">
+        <v>46257</v>
+      </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
+      <c r="E22" s="5" t="s">
+        <v>137</v>
+      </c>
       <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
+      <c r="G22" s="5">
+        <v>1000</v>
+      </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5">
         <f t="shared" si="1"/>
-        <v>24756</v>
+        <v>23756</v>
       </c>
       <c r="K22" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4843,18 +4885,26 @@
       <c r="N22" s="5"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="5"/>
-      <c r="B23" s="9"/>
+      <c r="A23" s="5">
+        <v>111</v>
+      </c>
+      <c r="B23" s="9">
+        <v>46257</v>
+      </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
+      <c r="E23" s="5" t="s">
+        <v>138</v>
+      </c>
       <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
+      <c r="G23" s="5">
+        <v>1500</v>
+      </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5">
         <f t="shared" si="1"/>
-        <v>24756</v>
+        <v>22256</v>
       </c>
       <c r="K23" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4865,18 +4915,26 @@
       <c r="N23" s="5"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="5"/>
-      <c r="B24" s="9"/>
+      <c r="A24" s="5">
+        <v>112</v>
+      </c>
+      <c r="B24" s="9">
+        <v>46258</v>
+      </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
+      <c r="E24" s="5" t="s">
+        <v>139</v>
+      </c>
       <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
+      <c r="G24" s="5">
+        <v>380</v>
+      </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="5">
         <f t="shared" si="1"/>
-        <v>24756</v>
+        <v>21876</v>
       </c>
       <c r="K24" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4887,18 +4945,26 @@
       <c r="N24" s="5"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="5"/>
-      <c r="B25" s="9"/>
+      <c r="A25" s="5">
+        <v>113</v>
+      </c>
+      <c r="B25" s="9">
+        <v>46258</v>
+      </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
+      <c r="E25" s="5" t="s">
+        <v>140</v>
+      </c>
       <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
+      <c r="G25" s="5">
+        <v>2000</v>
+      </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5">
         <f t="shared" si="1"/>
-        <v>24756</v>
+        <v>19876</v>
       </c>
       <c r="K25" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4910,17 +4976,23 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="5"/>
-      <c r="B26" s="9"/>
+      <c r="B26" s="9">
+        <v>46258</v>
+      </c>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
+      <c r="E26" s="5" t="s">
+        <v>141</v>
+      </c>
       <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
+      <c r="G26" s="5">
+        <v>1000</v>
+      </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
       <c r="J26" s="5">
         <f t="shared" si="1"/>
-        <v>24756</v>
+        <v>18876</v>
       </c>
       <c r="K26" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4932,17 +5004,23 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="5"/>
-      <c r="B27" s="9"/>
+      <c r="B27" s="9">
+        <v>46258</v>
+      </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
+      <c r="E27" s="5" t="s">
+        <v>142</v>
+      </c>
       <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
+      <c r="G27" s="5">
+        <v>500</v>
+      </c>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5">
         <f t="shared" si="1"/>
-        <v>24756</v>
+        <v>18376</v>
       </c>
       <c r="K27" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4964,7 +5042,7 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5">
         <f t="shared" si="1"/>
-        <v>24756</v>
+        <v>18376</v>
       </c>
       <c r="K28" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4986,7 +5064,7 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5">
         <f t="shared" si="1"/>
-        <v>24756</v>
+        <v>18376</v>
       </c>
       <c r="K29" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5008,7 +5086,7 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5">
         <f t="shared" si="1"/>
-        <v>24756</v>
+        <v>18376</v>
       </c>
       <c r="K30" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5030,7 +5108,7 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5">
         <f t="shared" si="1"/>
-        <v>24756</v>
+        <v>18376</v>
       </c>
       <c r="K31" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5052,7 +5130,7 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5">
         <f t="shared" si="1"/>
-        <v>24756</v>
+        <v>18376</v>
       </c>
       <c r="K32" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5074,7 +5152,7 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5">
         <f t="shared" si="1"/>
-        <v>24756</v>
+        <v>18376</v>
       </c>
       <c r="K33" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5096,7 +5174,7 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5">
         <f t="shared" si="1"/>
-        <v>24756</v>
+        <v>18376</v>
       </c>
       <c r="K34" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5117,7 +5195,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="6">
         <f>SUM(G4:G34)</f>
-        <v>337184</v>
+        <v>343564</v>
       </c>
       <c r="H35" s="6">
         <f>SUM(H4:H34)</f>
@@ -5129,24 +5207,6 @@
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="G37">
-        <f>25000+150+145</f>
-        <v>25295</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="G38">
-        <f>J34-G37</f>
-        <v>-539</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="G39">
-        <f>10914-G38</f>
-        <v>11453</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/سجل الايرادات والمصروفات (version 1).xlsb.xlsx
+++ b/سجل الايرادات والمصروفات (version 1).xlsb.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Henu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FF8003-D992-4AD4-BA33-27E676F9D2F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614AA8E6-3E88-4DD9-8A68-FF601A26A55C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{B3249B00-A14B-4484-9177-C0A03E3FFFA3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{B3249B00-A14B-4484-9177-C0A03E3FFFA3}"/>
   </bookViews>
   <sheets>
     <sheet name="1-A Petty Cash" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
     <sheet name="1-B Petty Cash" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="153">
   <si>
     <t>هوستل الأهرامات — سجل حركة صندوق المصروفات النثرية</t>
   </si>
@@ -471,6 +472,36 @@
   </si>
   <si>
     <t>سلفة من الراتب مدحت</t>
+  </si>
+  <si>
+    <t>تغيير حوض حمام 301 وتغيير واصلاح خلاط اللحوض</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تمويل من المالك انستاباي </t>
+  </si>
+  <si>
+    <t>تم التحويل على دفعتين 5000 ثم 100000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مستلزمات السباكة حسب الفاتورة </t>
+  </si>
+  <si>
+    <t>نقل مستلزمات السباكة</t>
+  </si>
+  <si>
+    <t>تمويل من المالك تحويل بنكي</t>
+  </si>
+  <si>
+    <t>دفعة من مصنعية النقاش</t>
+  </si>
+  <si>
+    <t>مصنعية السباك</t>
+  </si>
+  <si>
+    <t>مستلزمات النقاشة</t>
+  </si>
+  <si>
+    <t>جزء  من حساب المغسلة</t>
   </si>
 </sst>
 </file>
@@ -584,7 +615,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -606,6 +637,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4975,7 +5008,9 @@
       <c r="N25" s="5"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="5"/>
+      <c r="A26" s="5">
+        <v>114</v>
+      </c>
       <c r="B26" s="9">
         <v>46258</v>
       </c>
@@ -5003,7 +5038,9 @@
       <c r="N26" s="5"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="5"/>
+      <c r="A27" s="5">
+        <v>115</v>
+      </c>
       <c r="B27" s="9">
         <v>46258</v>
       </c>
@@ -5021,6 +5058,899 @@
       <c r="J27" s="5">
         <f t="shared" si="1"/>
         <v>18376</v>
+      </c>
+      <c r="K27" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A28" s="5">
+        <v>116</v>
+      </c>
+      <c r="B28" s="9">
+        <v>46258</v>
+      </c>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5">
+        <v>500</v>
+      </c>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5">
+        <f t="shared" si="1"/>
+        <v>17876</v>
+      </c>
+      <c r="K28" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A29" s="5">
+        <v>117</v>
+      </c>
+      <c r="B29" s="9">
+        <v>46259</v>
+      </c>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5">
+        <v>15000</v>
+      </c>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5">
+        <f t="shared" si="1"/>
+        <v>32876</v>
+      </c>
+      <c r="K29" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A30" s="5">
+        <v>118</v>
+      </c>
+      <c r="B30" s="9">
+        <v>46259</v>
+      </c>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5">
+        <v>20150</v>
+      </c>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5">
+        <f>J29-G30+H30</f>
+        <v>12726</v>
+      </c>
+      <c r="K30" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A31" s="5">
+        <v>119</v>
+      </c>
+      <c r="B31" s="9">
+        <v>46259</v>
+      </c>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5">
+        <v>350</v>
+      </c>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5">
+        <f>J30-G31+H31</f>
+        <v>12376</v>
+      </c>
+      <c r="K31" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A32" s="5">
+        <v>120</v>
+      </c>
+      <c r="B32" s="9">
+        <v>46259</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5">
+        <v>15000</v>
+      </c>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5">
+        <f t="shared" si="1"/>
+        <v>27376</v>
+      </c>
+      <c r="K32" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A33" s="5">
+        <v>121</v>
+      </c>
+      <c r="B33" s="9">
+        <v>46259</v>
+      </c>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5">
+        <v>2000</v>
+      </c>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5">
+        <f t="shared" si="1"/>
+        <v>25376</v>
+      </c>
+      <c r="K33" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A34" s="5">
+        <v>122</v>
+      </c>
+      <c r="B34" s="9">
+        <v>46259</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5">
+        <v>8000</v>
+      </c>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5">
+        <f t="shared" si="1"/>
+        <v>17376</v>
+      </c>
+      <c r="K34" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A35" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6">
+        <f>SUM(G4:G34)</f>
+        <v>374564</v>
+      </c>
+      <c r="H35" s="6">
+        <f>SUM(H4:H34)</f>
+        <v>391940</v>
+      </c>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC0DD83B-4B1E-47CB-9675-457EE4823204}">
+  <dimension ref="A1:N35"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="69" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="7">
+        <v>5000</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="18">
+        <f>Sheet2!G35</f>
+        <v>374564</v>
+      </c>
+      <c r="H4" s="18">
+        <f>Sheet2!H35</f>
+        <v>391940</v>
+      </c>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12">
+        <f>C4-G4+H4</f>
+        <v>17376</v>
+      </c>
+      <c r="K4" s="12" t="str">
+        <f t="shared" ref="K4:K34" si="0">IF(J4&lt;200,"تنبيه: اعد التعبئة","مقبول")</f>
+        <v>مقبول</v>
+      </c>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A5" s="5">
+        <v>123</v>
+      </c>
+      <c r="B5" s="9">
+        <v>46259</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5">
+        <v>5500</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5">
+        <f t="shared" ref="J5:J34" si="1">J4-G5+H5</f>
+        <v>11876</v>
+      </c>
+      <c r="K5" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A6" s="5">
+        <v>124</v>
+      </c>
+      <c r="B6" s="9">
+        <v>46259</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5">
+        <v>1000</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5">
+        <f t="shared" si="1"/>
+        <v>10876</v>
+      </c>
+      <c r="K6" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A7" s="5"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5">
+        <f t="shared" si="1"/>
+        <v>10876</v>
+      </c>
+      <c r="K7" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A8" s="5"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5">
+        <f t="shared" si="1"/>
+        <v>10876</v>
+      </c>
+      <c r="K8" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A9" s="5"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5">
+        <f t="shared" si="1"/>
+        <v>10876</v>
+      </c>
+      <c r="K9" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A10" s="5"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5">
+        <f t="shared" si="1"/>
+        <v>10876</v>
+      </c>
+      <c r="K10" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A11" s="5"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5">
+        <f t="shared" si="1"/>
+        <v>10876</v>
+      </c>
+      <c r="K11" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A12" s="5"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5">
+        <f t="shared" si="1"/>
+        <v>10876</v>
+      </c>
+      <c r="K12" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" s="5"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5">
+        <f t="shared" si="1"/>
+        <v>10876</v>
+      </c>
+      <c r="K13" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A14" s="5"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5">
+        <f t="shared" si="1"/>
+        <v>10876</v>
+      </c>
+      <c r="K14" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15" s="5"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5">
+        <f t="shared" si="1"/>
+        <v>10876</v>
+      </c>
+      <c r="K15" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" s="5"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5">
+        <f t="shared" si="1"/>
+        <v>10876</v>
+      </c>
+      <c r="K16" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A17" s="5"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5">
+        <f t="shared" si="1"/>
+        <v>10876</v>
+      </c>
+      <c r="K17" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A18" s="5"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5">
+        <f t="shared" si="1"/>
+        <v>10876</v>
+      </c>
+      <c r="K18" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A19" s="5"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5">
+        <f t="shared" si="1"/>
+        <v>10876</v>
+      </c>
+      <c r="K19" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A20" s="5"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5">
+        <f t="shared" si="1"/>
+        <v>10876</v>
+      </c>
+      <c r="K20" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A21" s="5"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5">
+        <f t="shared" si="1"/>
+        <v>10876</v>
+      </c>
+      <c r="K21" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A22" s="5"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5">
+        <f t="shared" si="1"/>
+        <v>10876</v>
+      </c>
+      <c r="K22" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A23" s="5"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5">
+        <f t="shared" si="1"/>
+        <v>10876</v>
+      </c>
+      <c r="K23" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A24" s="5"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5">
+        <f t="shared" si="1"/>
+        <v>10876</v>
+      </c>
+      <c r="K24" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A25" s="5"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5">
+        <f t="shared" si="1"/>
+        <v>10876</v>
+      </c>
+      <c r="K25" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A26" s="5"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5">
+        <f t="shared" si="1"/>
+        <v>10876</v>
+      </c>
+      <c r="K26" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>مقبول</v>
+      </c>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A27" s="5"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5">
+        <f t="shared" si="1"/>
+        <v>10876</v>
       </c>
       <c r="K27" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5042,7 +5972,7 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5">
         <f t="shared" si="1"/>
-        <v>18376</v>
+        <v>10876</v>
       </c>
       <c r="K28" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5064,7 +5994,7 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5">
         <f t="shared" si="1"/>
-        <v>18376</v>
+        <v>10876</v>
       </c>
       <c r="K29" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5085,8 +6015,8 @@
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="5">
-        <f t="shared" si="1"/>
-        <v>18376</v>
+        <f>J29-G30+H30</f>
+        <v>10876</v>
       </c>
       <c r="K30" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5101,14 +6031,14 @@
       <c r="B31" s="9"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
+      <c r="E31" s="17"/>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5">
-        <f t="shared" si="1"/>
-        <v>18376</v>
+        <f>J30-G31+H31</f>
+        <v>10876</v>
       </c>
       <c r="K31" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5130,7 +6060,7 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5">
         <f t="shared" si="1"/>
-        <v>18376</v>
+        <v>10876</v>
       </c>
       <c r="K32" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5152,7 +6082,7 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5">
         <f t="shared" si="1"/>
-        <v>18376</v>
+        <v>10876</v>
       </c>
       <c r="K33" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5174,7 +6104,7 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5">
         <f t="shared" si="1"/>
-        <v>18376</v>
+        <v>10876</v>
       </c>
       <c r="K34" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5195,11 +6125,11 @@
       <c r="F35" s="6"/>
       <c r="G35" s="6">
         <f>SUM(G4:G34)</f>
-        <v>343564</v>
+        <v>381064</v>
       </c>
       <c r="H35" s="6">
         <f>SUM(H4:H34)</f>
-        <v>361940</v>
+        <v>391940</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>

--- a/سجل الايرادات والمصروفات (version 1).xlsb.xlsx
+++ b/سجل الايرادات والمصروفات (version 1).xlsb.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Henu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614AA8E6-3E88-4DD9-8A68-FF601A26A55C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6165CE0C-1713-437D-A6D6-B3AD2F6161BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{B3249B00-A14B-4484-9177-C0A03E3FFFA3}"/>
   </bookViews>
@@ -20,6 +20,7 @@
     <sheet name="Sheet3" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="175">
   <si>
     <t>هوستل الأهرامات — سجل حركة صندوق المصروفات النثرية</t>
   </si>
@@ -237,9 +238,6 @@
     <t>دفعة باقي 300</t>
   </si>
   <si>
-    <t xml:space="preserve">تحويل انستا من رأس المال </t>
-  </si>
-  <si>
     <t xml:space="preserve">دفعة 50% لشركة كوين للمفروشات </t>
   </si>
   <si>
@@ -369,27 +367,18 @@
     <t>ملة سرير 160سم للجناح</t>
   </si>
   <si>
-    <t>اطباق واكواب من امازون</t>
-  </si>
-  <si>
     <t xml:space="preserve">حساب النجار تقفيل كل شغل النجارة </t>
   </si>
   <si>
     <t>تقفيل كل الحساب القديم</t>
   </si>
   <si>
-    <t>ماء وسوفت درينك للحفلة</t>
-  </si>
-  <si>
     <t>مشتريات نسكافيه ومنظفات وعصائر</t>
   </si>
   <si>
     <t>مبيت يوسف</t>
   </si>
   <si>
-    <t>تمويل من المالك لشراء امواب واطباق</t>
-  </si>
-  <si>
     <t xml:space="preserve">غسيل السجاد </t>
   </si>
   <si>
@@ -441,9 +430,6 @@
     <t xml:space="preserve">باقي 13230 دفعة اخيرة وتم استلام كل الطلبية اذن تسليم رقم بيان سعر رقم 4113 بتاريخ 22 اغسطس </t>
   </si>
   <si>
-    <t>عهدة الاستقبال</t>
-  </si>
-  <si>
     <t>حسب الكشف المرفق</t>
   </si>
   <si>
@@ -502,6 +488,87 @@
   </si>
   <si>
     <t>جزء  من حساب المغسلة</t>
+  </si>
+  <si>
+    <t>سلفة لخالد</t>
+  </si>
+  <si>
+    <t>كارتونة مياه</t>
+  </si>
+  <si>
+    <t>مستلزمات كهرباء</t>
+  </si>
+  <si>
+    <t>مواصلات ونقل  مستلزمات الكهرباء</t>
+  </si>
+  <si>
+    <t>ادوات نظافة</t>
+  </si>
+  <si>
+    <t>تحت حساب شبابيك السلم</t>
+  </si>
+  <si>
+    <t>تحت حساب مصنعية الكهرباء</t>
+  </si>
+  <si>
+    <t>باقي طلبات النقاش</t>
+  </si>
+  <si>
+    <t>سلفة ل منة</t>
+  </si>
+  <si>
+    <t>سلفة ل يوسف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بن </t>
+  </si>
+  <si>
+    <t>منظفات</t>
+  </si>
+  <si>
+    <t>سلفة من الراتب محمد منسي</t>
+  </si>
+  <si>
+    <t>تحت حساب سلوك ووصلات الدش والنت</t>
+  </si>
+  <si>
+    <t>تحت حساب الويبسايت</t>
+  </si>
+  <si>
+    <t>بخور</t>
+  </si>
+  <si>
+    <t>مغسلة</t>
+  </si>
+  <si>
+    <t>تم غسيل كل المفروشات والسجاد</t>
+  </si>
+  <si>
+    <t>سلفة ل جومانا</t>
+  </si>
+  <si>
+    <t>كرتونة ماء</t>
+  </si>
+  <si>
+    <t>صابون بريل</t>
+  </si>
+  <si>
+    <t>معدات نظافة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">باقي مصنعية النقاش </t>
+  </si>
+  <si>
+    <t>اطباق واكواب من امازون صيني وزجاج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ماء وسوفت درينك </t>
+  </si>
+  <si>
+    <t>شراء الوان لرسم اللوحات</t>
+  </si>
+  <si>
+    <t>سلفة من الراتب يوسف</t>
   </si>
 </sst>
 </file>
@@ -615,7 +682,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -631,14 +698,13 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1010,22 +1076,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="38" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
@@ -2100,22 +2166,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
@@ -2606,31 +2672,17 @@
       <c r="N17" s="5"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="5">
-        <v>45</v>
-      </c>
-      <c r="B18" s="9">
-        <v>46246</v>
-      </c>
+      <c r="A18" s="5"/>
+      <c r="B18" s="9"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
-      <c r="E18" s="5" t="s">
-        <v>64</v>
-      </c>
+      <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
-      <c r="H18" s="5">
-        <v>10000</v>
-      </c>
+      <c r="H18" s="5"/>
       <c r="I18" s="5"/>
-      <c r="J18" s="5">
-        <f t="shared" si="0"/>
-        <v>16325</v>
-      </c>
-      <c r="K18" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>مقبول</v>
-      </c>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
@@ -2645,7 +2697,7 @@
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5">
@@ -2655,14 +2707,14 @@
       <c r="I19" s="5"/>
       <c r="J19" s="5">
         <f t="shared" si="0"/>
-        <v>9495</v>
+        <v>-6830</v>
       </c>
       <c r="K19" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>مقبول</v>
+        <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="L19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
@@ -2677,7 +2729,7 @@
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -2687,11 +2739,11 @@
       <c r="I20" s="5"/>
       <c r="J20" s="5">
         <f t="shared" si="0"/>
-        <v>9710</v>
+        <v>-6615</v>
       </c>
       <c r="K20" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>مقبول</v>
+        <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
@@ -2707,7 +2759,7 @@
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -2717,11 +2769,11 @@
       <c r="I21" s="5"/>
       <c r="J21" s="5">
         <f t="shared" si="0"/>
-        <v>9970</v>
+        <v>-6355</v>
       </c>
       <c r="K21" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>مقبول</v>
+        <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
@@ -2737,7 +2789,7 @@
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5">
@@ -2747,14 +2799,14 @@
       <c r="I22" s="5"/>
       <c r="J22" s="5">
         <f t="shared" si="0"/>
-        <v>4720</v>
+        <v>-11605</v>
       </c>
       <c r="K22" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>مقبول</v>
+        <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
@@ -2769,7 +2821,7 @@
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5">
@@ -2779,14 +2831,14 @@
       <c r="I23" s="5"/>
       <c r="J23" s="5">
         <f t="shared" si="0"/>
-        <v>-580</v>
+        <v>-16905</v>
       </c>
       <c r="K23" s="5" t="str">
         <f t="shared" si="1"/>
         <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
@@ -2801,7 +2853,7 @@
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -2811,14 +2863,14 @@
       <c r="I24" s="5"/>
       <c r="J24" s="5">
         <f t="shared" si="0"/>
-        <v>9970</v>
+        <v>-6355</v>
       </c>
       <c r="K24" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>مقبول</v>
+        <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
@@ -2833,7 +2885,7 @@
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5">
@@ -2843,11 +2895,11 @@
       <c r="I25" s="5"/>
       <c r="J25" s="5">
         <f t="shared" si="0"/>
-        <v>9870</v>
+        <v>-6455</v>
       </c>
       <c r="K25" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>مقبول</v>
+        <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
@@ -2873,11 +2925,11 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5">
         <f t="shared" si="0"/>
-        <v>9670</v>
+        <v>-6655</v>
       </c>
       <c r="K26" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>مقبول</v>
+        <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
@@ -2893,7 +2945,7 @@
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5">
@@ -2903,11 +2955,11 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5">
         <f t="shared" si="0"/>
-        <v>9400</v>
+        <v>-6925</v>
       </c>
       <c r="K27" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>مقبول</v>
+        <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
@@ -2923,7 +2975,7 @@
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5">
@@ -2933,11 +2985,11 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5">
         <f t="shared" si="0"/>
-        <v>9330</v>
+        <v>-6995</v>
       </c>
       <c r="K28" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>مقبول</v>
+        <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
@@ -2953,7 +3005,7 @@
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5">
@@ -2963,11 +3015,11 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5">
         <f t="shared" si="0"/>
-        <v>9265</v>
+        <v>-7060</v>
       </c>
       <c r="K29" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>مقبول</v>
+        <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
@@ -2983,7 +3035,7 @@
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -2993,14 +3045,14 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5">
         <f t="shared" si="0"/>
-        <v>59435</v>
+        <v>43110</v>
       </c>
       <c r="K30" s="5" t="str">
         <f t="shared" si="1"/>
         <v>مقبول</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
@@ -3015,7 +3067,7 @@
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5">
@@ -3025,7 +3077,7 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5">
         <f t="shared" si="0"/>
-        <v>42130</v>
+        <v>25805</v>
       </c>
       <c r="K31" s="5" t="str">
         <f t="shared" si="1"/>
@@ -3045,7 +3097,7 @@
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5">
@@ -3055,7 +3107,7 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5">
         <f t="shared" si="0"/>
-        <v>41130</v>
+        <v>24805</v>
       </c>
       <c r="K32" s="5" t="str">
         <f t="shared" si="1"/>
@@ -3075,7 +3127,7 @@
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5">
@@ -3085,7 +3137,7 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5">
         <f t="shared" si="0"/>
-        <v>40630</v>
+        <v>24305</v>
       </c>
       <c r="K33" s="5" t="str">
         <f t="shared" si="1"/>
@@ -3103,7 +3155,7 @@
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5">
@@ -3113,7 +3165,7 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5">
         <f t="shared" si="0"/>
-        <v>36730</v>
+        <v>20405</v>
       </c>
       <c r="K34" s="5" t="str">
         <f t="shared" si="1"/>
@@ -3138,7 +3190,7 @@
       </c>
       <c r="H35" s="6">
         <f>SUM(H4:H34)</f>
-        <v>157415</v>
+        <v>147415</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
@@ -3157,7 +3209,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBE875E9-EAA8-45FD-BC55-93704B641099}">
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.90625" bestFit="1" customWidth="1"/>
@@ -3175,22 +3227,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
@@ -3268,17 +3320,17 @@
       <c r="E4" s="14"/>
       <c r="F4" s="12"/>
       <c r="G4" s="12">
-        <f>'1-A Petty Cash'!G36</f>
-        <v>42809</v>
+        <f>Sheet1!G35</f>
+        <v>120685</v>
       </c>
       <c r="H4" s="12">
-        <f>'1-A Petty Cash'!H36</f>
-        <v>78020</v>
+        <f>Sheet1!H35</f>
+        <v>147415</v>
       </c>
       <c r="I4" s="12"/>
       <c r="J4" s="12">
         <f>C4-G4+H4</f>
-        <v>35211</v>
+        <v>26730</v>
       </c>
       <c r="K4" s="12" t="str">
         <f t="shared" ref="K4:K34" si="0">IF(J4&lt;200,"تنبيه: اعد التعبئة","مقبول")</f>
@@ -3298,7 +3350,7 @@
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5">
@@ -3308,7 +3360,7 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5">
         <f t="shared" ref="J5:J34" si="1">J4-G5+H5</f>
-        <v>34801</v>
+        <v>26320</v>
       </c>
       <c r="K5" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3328,7 +3380,7 @@
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5">
@@ -3338,7 +3390,7 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5">
         <f t="shared" si="1"/>
-        <v>34716</v>
+        <v>26235</v>
       </c>
       <c r="K6" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3358,7 +3410,7 @@
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5">
@@ -3368,7 +3420,7 @@
       <c r="I7" s="5"/>
       <c r="J7" s="5">
         <f t="shared" si="1"/>
-        <v>34516</v>
+        <v>26035</v>
       </c>
       <c r="K7" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3388,7 +3440,7 @@
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="10" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5">
@@ -3398,14 +3450,14 @@
       <c r="I8" s="5"/>
       <c r="J8" s="5">
         <f t="shared" si="1"/>
-        <v>33516</v>
+        <v>25035</v>
       </c>
       <c r="K8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>مقبول</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
@@ -3420,7 +3472,7 @@
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5">
@@ -3430,7 +3482,7 @@
       <c r="I9" s="5"/>
       <c r="J9" s="5">
         <f t="shared" si="1"/>
-        <v>33166</v>
+        <v>24685</v>
       </c>
       <c r="K9" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3450,7 +3502,7 @@
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5">
@@ -3460,14 +3512,14 @@
       <c r="I10" s="5"/>
       <c r="J10" s="5">
         <f t="shared" si="1"/>
-        <v>30666</v>
+        <v>22185</v>
       </c>
       <c r="K10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>مقبول</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
@@ -3482,7 +3534,7 @@
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5">
@@ -3492,14 +3544,14 @@
       <c r="I11" s="5"/>
       <c r="J11" s="5">
         <f t="shared" si="1"/>
-        <v>29666</v>
+        <v>21185</v>
       </c>
       <c r="K11" s="5" t="str">
         <f t="shared" si="0"/>
         <v>مقبول</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
@@ -3514,7 +3566,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5">
@@ -3524,7 +3576,7 @@
       <c r="I12" s="5"/>
       <c r="J12" s="5">
         <f t="shared" si="1"/>
-        <v>29016</v>
+        <v>20535</v>
       </c>
       <c r="K12" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3544,7 +3596,7 @@
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -3554,7 +3606,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5">
         <f t="shared" si="1"/>
-        <v>149016</v>
+        <v>140535</v>
       </c>
       <c r="K13" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3574,7 +3626,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -3584,7 +3636,7 @@
       <c r="I14" s="5"/>
       <c r="J14" s="5">
         <f t="shared" si="1"/>
-        <v>279536</v>
+        <v>271055</v>
       </c>
       <c r="K14" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3604,7 +3656,7 @@
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5">
@@ -3614,7 +3666,7 @@
       <c r="I15" s="5"/>
       <c r="J15" s="5">
         <f t="shared" si="1"/>
-        <v>279266</v>
+        <v>270785</v>
       </c>
       <c r="K15" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3634,7 +3686,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -3644,7 +3696,7 @@
       <c r="I16" s="5"/>
       <c r="J16" s="5">
         <f t="shared" si="1"/>
-        <v>281266</v>
+        <v>272785</v>
       </c>
       <c r="K16" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3664,7 +3716,7 @@
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5">
@@ -3674,7 +3726,7 @@
       <c r="I17" s="5"/>
       <c r="J17" s="5">
         <f t="shared" si="1"/>
-        <v>61266</v>
+        <v>52785</v>
       </c>
       <c r="K17" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3694,7 +3746,7 @@
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5">
@@ -3704,13 +3756,15 @@
       <c r="I18" s="5"/>
       <c r="J18" s="5">
         <f t="shared" si="1"/>
-        <v>60266</v>
+        <v>51785</v>
       </c>
       <c r="K18" s="5" t="str">
         <f t="shared" si="0"/>
         <v>مقبول</v>
       </c>
-      <c r="L18" s="5"/>
+      <c r="L18" s="5" t="s">
+        <v>97</v>
+      </c>
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
     </row>
@@ -3724,7 +3778,7 @@
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5">
@@ -3734,7 +3788,7 @@
       <c r="I19" s="5"/>
       <c r="J19" s="5">
         <f t="shared" si="1"/>
-        <v>59266</v>
+        <v>50785</v>
       </c>
       <c r="K19" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3753,7 +3807,7 @@
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5">
@@ -3763,7 +3817,7 @@
       <c r="I20" s="5"/>
       <c r="J20" s="5">
         <f t="shared" si="1"/>
-        <v>59166</v>
+        <v>50685</v>
       </c>
       <c r="K20" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3783,7 +3837,7 @@
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5">
@@ -3793,7 +3847,7 @@
       <c r="I21" s="5"/>
       <c r="J21" s="5">
         <f t="shared" si="1"/>
-        <v>58866</v>
+        <v>50385</v>
       </c>
       <c r="K21" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3813,7 +3867,7 @@
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5">
@@ -3823,7 +3877,7 @@
       <c r="I22" s="5"/>
       <c r="J22" s="5">
         <f t="shared" si="1"/>
-        <v>58366</v>
+        <v>49885</v>
       </c>
       <c r="K22" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3843,7 +3897,7 @@
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -3853,14 +3907,14 @@
       <c r="I23" s="5"/>
       <c r="J23" s="5">
         <f t="shared" si="1"/>
-        <v>78366</v>
+        <v>69885</v>
       </c>
       <c r="K23" s="5" t="str">
         <f t="shared" si="0"/>
         <v>مقبول</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
@@ -3875,7 +3929,7 @@
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5">
@@ -3885,7 +3939,7 @@
       <c r="I24" s="5"/>
       <c r="J24" s="5">
         <f t="shared" si="1"/>
-        <v>76466</v>
+        <v>67985</v>
       </c>
       <c r="K24" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3905,7 +3959,7 @@
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5">
@@ -3915,7 +3969,7 @@
       <c r="I25" s="5"/>
       <c r="J25" s="5">
         <f t="shared" si="1"/>
-        <v>76366</v>
+        <v>67885</v>
       </c>
       <c r="K25" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3935,7 +3989,7 @@
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5">
@@ -3945,7 +3999,7 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5">
         <f t="shared" si="1"/>
-        <v>75266</v>
+        <v>66785</v>
       </c>
       <c r="K26" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3965,7 +4019,7 @@
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>108</v>
+        <v>171</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5">
@@ -3975,7 +4029,7 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5">
         <f t="shared" si="1"/>
-        <v>65966</v>
+        <v>57485</v>
       </c>
       <c r="K27" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3995,7 +4049,7 @@
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5">
@@ -4005,14 +4059,14 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5">
         <f t="shared" si="1"/>
-        <v>65566</v>
+        <v>57085</v>
       </c>
       <c r="K28" s="5" t="str">
         <f t="shared" si="0"/>
         <v>مقبول</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
@@ -4027,7 +4081,7 @@
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>111</v>
+        <v>172</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5">
@@ -4037,7 +4091,7 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5">
         <f t="shared" si="1"/>
-        <v>64901</v>
+        <v>56420</v>
       </c>
       <c r="K29" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4057,7 +4111,7 @@
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5">
@@ -4067,7 +4121,7 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5">
         <f t="shared" si="1"/>
-        <v>64001</v>
+        <v>55520</v>
       </c>
       <c r="K30" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4087,7 +4141,7 @@
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5">
@@ -4097,7 +4151,7 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5">
         <f t="shared" si="1"/>
-        <v>63801</v>
+        <v>55320</v>
       </c>
       <c r="K31" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4117,7 +4171,7 @@
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -4127,14 +4181,14 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5">
         <f t="shared" si="1"/>
-        <v>73101</v>
+        <v>64620</v>
       </c>
       <c r="K32" s="5" t="str">
         <f t="shared" si="0"/>
         <v>مقبول</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
@@ -4149,7 +4203,7 @@
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5">
@@ -4159,7 +4213,7 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5">
         <f t="shared" si="1"/>
-        <v>72841</v>
+        <v>64360</v>
       </c>
       <c r="K33" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4179,7 +4233,7 @@
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5">
@@ -4189,7 +4243,7 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5">
         <f t="shared" si="1"/>
-        <v>72641</v>
+        <v>64160</v>
       </c>
       <c r="K34" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4210,11 +4264,11 @@
       <c r="F35" s="6"/>
       <c r="G35" s="6">
         <f>SUM(G4:G34)</f>
-        <v>287199</v>
+        <v>365075</v>
       </c>
       <c r="H35" s="6">
         <f>SUM(H4:H34)</f>
-        <v>359840</v>
+        <v>429235</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
@@ -4222,18 +4276,6 @@
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="H37">
-        <f>55000+6830</f>
-        <v>61830</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="H38">
-        <f>J34-H37</f>
-        <v>10811</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4263,22 +4305,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
@@ -4357,16 +4399,16 @@
       <c r="F4" s="12"/>
       <c r="G4" s="12">
         <f>'1-B Petty Cash'!G35</f>
-        <v>287199</v>
+        <v>365075</v>
       </c>
       <c r="H4" s="12">
         <f>'1-B Petty Cash'!H35</f>
-        <v>359840</v>
+        <v>429235</v>
       </c>
       <c r="I4" s="12"/>
       <c r="J4" s="12">
         <f>C4-G4+H4</f>
-        <v>72641</v>
+        <v>64160</v>
       </c>
       <c r="K4" s="12" t="str">
         <f t="shared" ref="K4:K34" si="0">IF(J4&lt;200,"تنبيه: اعد التعبئة","مقبول")</f>
@@ -4386,7 +4428,7 @@
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="10" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5">
@@ -4396,7 +4438,7 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5">
         <f t="shared" ref="J5:J34" si="1">J4-G5+H5</f>
-        <v>72326</v>
+        <v>63845</v>
       </c>
       <c r="K5" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4416,7 +4458,7 @@
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5">
@@ -4426,7 +4468,7 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5">
         <f t="shared" si="1"/>
-        <v>72181</v>
+        <v>63700</v>
       </c>
       <c r="K6" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4446,7 +4488,7 @@
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5">
@@ -4456,7 +4498,7 @@
       <c r="I7" s="5"/>
       <c r="J7" s="5">
         <f t="shared" si="1"/>
-        <v>70281</v>
+        <v>61800</v>
       </c>
       <c r="K7" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4476,7 +4518,7 @@
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="10" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5">
@@ -4486,7 +4528,7 @@
       <c r="I8" s="5"/>
       <c r="J8" s="5">
         <f t="shared" si="1"/>
-        <v>70091</v>
+        <v>61610</v>
       </c>
       <c r="K8" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4506,7 +4548,7 @@
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5">
@@ -4516,7 +4558,7 @@
       <c r="I9" s="5"/>
       <c r="J9" s="5">
         <f t="shared" si="1"/>
-        <v>69946</v>
+        <v>61465</v>
       </c>
       <c r="K9" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4536,7 +4578,7 @@
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="10" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5">
@@ -4546,7 +4588,7 @@
       <c r="I10" s="5"/>
       <c r="J10" s="5">
         <f t="shared" si="1"/>
-        <v>67796</v>
+        <v>59315</v>
       </c>
       <c r="K10" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4566,7 +4608,7 @@
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5">
@@ -4576,7 +4618,7 @@
       <c r="I11" s="5"/>
       <c r="J11" s="5">
         <f t="shared" si="1"/>
-        <v>65776</v>
+        <v>57295</v>
       </c>
       <c r="K11" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4596,7 +4638,7 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="10" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5">
@@ -4606,7 +4648,7 @@
       <c r="I12" s="5"/>
       <c r="J12" s="5">
         <f t="shared" si="1"/>
-        <v>64806</v>
+        <v>56325</v>
       </c>
       <c r="K12" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4626,7 +4668,7 @@
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="10" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5">
@@ -4636,7 +4678,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5">
         <f t="shared" si="1"/>
-        <v>64606</v>
+        <v>56125</v>
       </c>
       <c r="K13" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4656,7 +4698,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5">
@@ -4666,7 +4708,7 @@
       <c r="I14" s="5"/>
       <c r="J14" s="5">
         <f t="shared" si="1"/>
-        <v>64556</v>
+        <v>56075</v>
       </c>
       <c r="K14" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4686,7 +4728,7 @@
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5">
@@ -4696,7 +4738,7 @@
       <c r="I15" s="5"/>
       <c r="J15" s="5">
         <f t="shared" si="1"/>
-        <v>64456</v>
+        <v>55975</v>
       </c>
       <c r="K15" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4716,7 +4758,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5">
@@ -4726,7 +4768,7 @@
       <c r="I16" s="5"/>
       <c r="J16" s="5">
         <f t="shared" si="1"/>
-        <v>64406</v>
+        <v>55925</v>
       </c>
       <c r="K16" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4746,7 +4788,7 @@
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -4756,7 +4798,7 @@
       <c r="I17" s="5"/>
       <c r="J17" s="5">
         <f t="shared" si="1"/>
-        <v>66506</v>
+        <v>58025</v>
       </c>
       <c r="K17" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4776,7 +4818,7 @@
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5">
@@ -4786,14 +4828,14 @@
       <c r="I18" s="5"/>
       <c r="J18" s="5">
         <f t="shared" si="1"/>
-        <v>36506</v>
+        <v>28025</v>
       </c>
       <c r="K18" s="5" t="str">
         <f t="shared" si="0"/>
         <v>مقبول</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
@@ -4807,18 +4849,14 @@
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
-      <c r="E19" s="5" t="s">
-        <v>132</v>
-      </c>
+      <c r="E19" s="5"/>
       <c r="F19" s="5"/>
-      <c r="G19" s="5">
-        <v>2000</v>
-      </c>
+      <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5">
         <f t="shared" si="1"/>
-        <v>34506</v>
+        <v>28025</v>
       </c>
       <c r="K19" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4837,7 +4875,7 @@
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5">
@@ -4847,7 +4885,7 @@
       <c r="I20" s="5"/>
       <c r="J20" s="5">
         <f t="shared" si="1"/>
-        <v>27256</v>
+        <v>20775</v>
       </c>
       <c r="K20" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4867,7 +4905,7 @@
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5">
@@ -4877,7 +4915,7 @@
       <c r="I21" s="5"/>
       <c r="J21" s="5">
         <f t="shared" si="1"/>
-        <v>24756</v>
+        <v>18275</v>
       </c>
       <c r="K21" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4897,7 +4935,7 @@
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5">
@@ -4907,7 +4945,7 @@
       <c r="I22" s="5"/>
       <c r="J22" s="5">
         <f t="shared" si="1"/>
-        <v>23756</v>
+        <v>17275</v>
       </c>
       <c r="K22" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4927,7 +4965,7 @@
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5">
@@ -4937,7 +4975,7 @@
       <c r="I23" s="5"/>
       <c r="J23" s="5">
         <f t="shared" si="1"/>
-        <v>22256</v>
+        <v>15775</v>
       </c>
       <c r="K23" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4957,7 +4995,7 @@
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5">
@@ -4967,7 +5005,7 @@
       <c r="I24" s="5"/>
       <c r="J24" s="5">
         <f t="shared" si="1"/>
-        <v>21876</v>
+        <v>15395</v>
       </c>
       <c r="K24" s="5" t="str">
         <f t="shared" si="0"/>
@@ -4987,7 +5025,7 @@
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5">
@@ -4997,7 +5035,7 @@
       <c r="I25" s="5"/>
       <c r="J25" s="5">
         <f t="shared" si="1"/>
-        <v>19876</v>
+        <v>13395</v>
       </c>
       <c r="K25" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5017,7 +5055,7 @@
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5">
@@ -5027,7 +5065,7 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5">
         <f t="shared" si="1"/>
-        <v>18876</v>
+        <v>12395</v>
       </c>
       <c r="K26" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5047,7 +5085,7 @@
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5">
@@ -5057,7 +5095,7 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5">
         <f t="shared" si="1"/>
-        <v>18376</v>
+        <v>11895</v>
       </c>
       <c r="K27" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5077,7 +5115,7 @@
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5">
@@ -5087,7 +5125,7 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5">
         <f t="shared" si="1"/>
-        <v>17876</v>
+        <v>11395</v>
       </c>
       <c r="K28" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5107,7 +5145,7 @@
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -5117,14 +5155,14 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5">
         <f t="shared" si="1"/>
-        <v>32876</v>
+        <v>26395</v>
       </c>
       <c r="K29" s="5" t="str">
         <f t="shared" si="0"/>
         <v>مقبول</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
@@ -5139,7 +5177,7 @@
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5">
@@ -5149,7 +5187,7 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5">
         <f>J29-G30+H30</f>
-        <v>12726</v>
+        <v>6245</v>
       </c>
       <c r="K30" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5168,8 +5206,8 @@
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
-      <c r="E31" s="17" t="s">
-        <v>147</v>
+      <c r="E31" s="11" t="s">
+        <v>142</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5">
@@ -5179,7 +5217,7 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5">
         <f>J30-G31+H31</f>
-        <v>12376</v>
+        <v>5895</v>
       </c>
       <c r="K31" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5199,7 +5237,7 @@
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -5209,7 +5247,7 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5">
         <f t="shared" si="1"/>
-        <v>27376</v>
+        <v>20895</v>
       </c>
       <c r="K32" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5229,7 +5267,7 @@
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5">
@@ -5239,7 +5277,7 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5">
         <f t="shared" si="1"/>
-        <v>25376</v>
+        <v>18895</v>
       </c>
       <c r="K33" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5259,7 +5297,7 @@
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
       <c r="E34" s="5" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5">
@@ -5269,7 +5307,7 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5">
         <f t="shared" si="1"/>
-        <v>17376</v>
+        <v>10895</v>
       </c>
       <c r="K34" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5290,11 +5328,11 @@
       <c r="F35" s="6"/>
       <c r="G35" s="6">
         <f>SUM(G4:G34)</f>
-        <v>374564</v>
+        <v>450440</v>
       </c>
       <c r="H35" s="6">
         <f>SUM(H4:H34)</f>
-        <v>391940</v>
+        <v>461335</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
@@ -5326,22 +5364,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
@@ -5418,18 +5456,18 @@
       <c r="D4" s="12"/>
       <c r="E4" s="14"/>
       <c r="F4" s="12"/>
-      <c r="G4" s="18">
+      <c r="G4" s="15">
         <f>Sheet2!G35</f>
-        <v>374564</v>
-      </c>
-      <c r="H4" s="18">
+        <v>450440</v>
+      </c>
+      <c r="H4" s="15">
         <f>Sheet2!H35</f>
-        <v>391940</v>
+        <v>461335</v>
       </c>
       <c r="I4" s="12"/>
       <c r="J4" s="12">
         <f>C4-G4+H4</f>
-        <v>17376</v>
+        <v>10895</v>
       </c>
       <c r="K4" s="12" t="str">
         <f t="shared" ref="K4:K34" si="0">IF(J4&lt;200,"تنبيه: اعد التعبئة","مقبول")</f>
@@ -5449,7 +5487,7 @@
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="10" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="5">
@@ -5459,7 +5497,7 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5">
         <f t="shared" ref="J5:J34" si="1">J4-G5+H5</f>
-        <v>11876</v>
+        <v>5395</v>
       </c>
       <c r="K5" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5479,7 +5517,7 @@
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5">
@@ -5489,7 +5527,7 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>4395</v>
       </c>
       <c r="K6" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5500,18 +5538,26 @@
       <c r="N6" s="5"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="5"/>
-      <c r="B7" s="9"/>
+      <c r="A7" s="5">
+        <v>125</v>
+      </c>
+      <c r="B7" s="9">
+        <v>46260</v>
+      </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="10"/>
+      <c r="E7" s="10" t="s">
+        <v>148</v>
+      </c>
       <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="G7" s="5">
+        <v>1500</v>
+      </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>2895</v>
       </c>
       <c r="K7" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5522,18 +5568,26 @@
       <c r="N7" s="5"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="5"/>
-      <c r="B8" s="9"/>
+      <c r="A8" s="5">
+        <v>126</v>
+      </c>
+      <c r="B8" s="9">
+        <v>46260</v>
+      </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
-      <c r="E8" s="10"/>
+      <c r="E8" s="10" t="s">
+        <v>149</v>
+      </c>
       <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
+      <c r="G8" s="5">
+        <v>140</v>
+      </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>2755</v>
       </c>
       <c r="K8" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5544,281 +5598,385 @@
       <c r="N8" s="5"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="5"/>
-      <c r="B9" s="9"/>
+      <c r="A9" s="5">
+        <v>127</v>
+      </c>
+      <c r="B9" s="9">
+        <v>46260</v>
+      </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
-      <c r="E9" s="10"/>
+      <c r="E9" s="10" t="s">
+        <v>150</v>
+      </c>
       <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="G9" s="5">
+        <v>3400</v>
+      </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
       <c r="J9" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>-645</v>
       </c>
       <c r="K9" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>مقبول</v>
+        <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="5"/>
-      <c r="B10" s="9"/>
+      <c r="A10" s="5">
+        <v>128</v>
+      </c>
+      <c r="B10" s="9">
+        <v>46260</v>
+      </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
-      <c r="E10" s="10"/>
+      <c r="E10" s="10" t="s">
+        <v>151</v>
+      </c>
       <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="G10" s="5">
+        <v>160</v>
+      </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>-805</v>
       </c>
       <c r="K10" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>مقبول</v>
+        <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="5"/>
-      <c r="B11" s="9"/>
+      <c r="A11" s="5">
+        <v>129</v>
+      </c>
+      <c r="B11" s="9">
+        <v>46261</v>
+      </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="10"/>
+      <c r="E11" s="10" t="s">
+        <v>152</v>
+      </c>
       <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="G11" s="5">
+        <v>100</v>
+      </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
       <c r="J11" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>-905</v>
       </c>
       <c r="K11" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>مقبول</v>
+        <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="5"/>
-      <c r="B12" s="9"/>
+      <c r="A12" s="5">
+        <v>130</v>
+      </c>
+      <c r="B12" s="9">
+        <v>46261</v>
+      </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="10"/>
+      <c r="E12" s="10" t="s">
+        <v>153</v>
+      </c>
       <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="G12" s="5">
+        <v>500</v>
+      </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>-1405</v>
       </c>
       <c r="K12" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>مقبول</v>
+        <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="5"/>
-      <c r="B13" s="9"/>
+      <c r="A13" s="5">
+        <v>131</v>
+      </c>
+      <c r="B13" s="9">
+        <v>46261</v>
+      </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
-      <c r="E13" s="10"/>
+      <c r="E13" s="10" t="s">
+        <v>154</v>
+      </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+      <c r="G13" s="5">
+        <v>500</v>
+      </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>-1905</v>
       </c>
       <c r="K13" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>مقبول</v>
+        <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="5"/>
-      <c r="B14" s="9"/>
+      <c r="A14" s="5">
+        <v>132</v>
+      </c>
+      <c r="B14" s="9">
+        <v>46261</v>
+      </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
+      <c r="E14" s="5" t="s">
+        <v>155</v>
+      </c>
       <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="G14" s="5">
+        <v>1520</v>
+      </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>-3425</v>
       </c>
       <c r="K14" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>مقبول</v>
+        <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="5"/>
-      <c r="B15" s="9"/>
+      <c r="A15" s="5">
+        <v>133</v>
+      </c>
+      <c r="B15" s="9">
+        <v>46262</v>
+      </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
+      <c r="E15" s="5" t="s">
+        <v>156</v>
+      </c>
       <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="G15" s="5">
+        <v>200</v>
+      </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>-3625</v>
       </c>
       <c r="K15" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>مقبول</v>
+        <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="5"/>
-      <c r="B16" s="9"/>
+      <c r="A16" s="5">
+        <v>134</v>
+      </c>
+      <c r="B16" s="9">
+        <v>46262</v>
+      </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
+      <c r="E16" s="5" t="s">
+        <v>157</v>
+      </c>
       <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
+      <c r="G16" s="5">
+        <v>150</v>
+      </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
       <c r="J16" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>-3775</v>
       </c>
       <c r="K16" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>مقبول</v>
+        <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="5"/>
-      <c r="B17" s="9"/>
+      <c r="A17" s="5">
+        <v>135</v>
+      </c>
+      <c r="B17" s="9">
+        <v>46263</v>
+      </c>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
+      <c r="E17" s="5" t="s">
+        <v>158</v>
+      </c>
       <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
+      <c r="G17" s="5">
+        <v>250</v>
+      </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>-4025</v>
       </c>
       <c r="K17" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>مقبول</v>
+        <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="5"/>
-      <c r="B18" s="9"/>
+      <c r="A18" s="5">
+        <v>136</v>
+      </c>
+      <c r="B18" s="9">
+        <v>46263</v>
+      </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
+      <c r="E18" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
+      <c r="G18" s="5">
+        <v>200</v>
+      </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>-4225</v>
       </c>
       <c r="K18" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>مقبول</v>
+        <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="5"/>
-      <c r="B19" s="9"/>
+      <c r="A19" s="5">
+        <v>137</v>
+      </c>
+      <c r="B19" s="9">
+        <v>46263</v>
+      </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
+      <c r="E19" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
+      <c r="G19" s="5">
+        <v>200</v>
+      </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>-4425</v>
       </c>
       <c r="K19" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>مقبول</v>
+        <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="5"/>
-      <c r="B20" s="9"/>
+      <c r="A20" s="5">
+        <v>138</v>
+      </c>
+      <c r="B20" s="9">
+        <v>46264</v>
+      </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
+      <c r="E20" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
+      <c r="G20" s="5">
+        <v>200</v>
+      </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>-4625</v>
       </c>
       <c r="K20" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>مقبول</v>
+        <v>تنبيه: اعد التعبئة</v>
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="5"/>
-      <c r="B21" s="9"/>
+      <c r="A21" s="5">
+        <v>139</v>
+      </c>
+      <c r="B21" s="9">
+        <v>46264</v>
+      </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
+      <c r="E21" s="5" t="s">
+        <v>77</v>
+      </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
+      <c r="H21" s="5">
+        <v>50000</v>
+      </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>45375</v>
       </c>
       <c r="K21" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5829,18 +5987,26 @@
       <c r="N21" s="5"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="5"/>
-      <c r="B22" s="9"/>
+      <c r="A22" s="5">
+        <v>140</v>
+      </c>
+      <c r="B22" s="9">
+        <v>46264</v>
+      </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
+      <c r="E22" s="5" t="s">
+        <v>161</v>
+      </c>
       <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
+      <c r="G22" s="5">
+        <v>20000</v>
+      </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>25375</v>
       </c>
       <c r="K22" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5851,18 +6017,26 @@
       <c r="N22" s="5"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="5"/>
-      <c r="B23" s="9"/>
+      <c r="A23" s="5">
+        <v>141</v>
+      </c>
+      <c r="B23" s="9">
+        <v>46264</v>
+      </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
+      <c r="E23" s="5" t="s">
+        <v>162</v>
+      </c>
       <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
+      <c r="G23" s="5">
+        <v>10000</v>
+      </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>15375</v>
       </c>
       <c r="K23" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5873,18 +6047,26 @@
       <c r="N23" s="5"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="5"/>
-      <c r="B24" s="9"/>
+      <c r="A24" s="5">
+        <v>142</v>
+      </c>
+      <c r="B24" s="9">
+        <v>46264</v>
+      </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
+      <c r="E24" s="5" t="s">
+        <v>163</v>
+      </c>
       <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
+      <c r="G24" s="5">
+        <v>100</v>
+      </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>15275</v>
       </c>
       <c r="K24" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5895,40 +6077,58 @@
       <c r="N24" s="5"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="5"/>
-      <c r="B25" s="9"/>
+      <c r="A25" s="5">
+        <v>143</v>
+      </c>
+      <c r="B25" s="9">
+        <v>46264</v>
+      </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
+      <c r="E25" s="5" t="s">
+        <v>164</v>
+      </c>
       <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
+      <c r="G25" s="5">
+        <v>2920</v>
+      </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>12355</v>
       </c>
       <c r="K25" s="5" t="str">
         <f t="shared" si="0"/>
         <v>مقبول</v>
       </c>
-      <c r="L25" s="5"/>
+      <c r="L25" s="5" t="s">
+        <v>165</v>
+      </c>
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="5"/>
-      <c r="B26" s="9"/>
+      <c r="A26" s="5">
+        <v>144</v>
+      </c>
+      <c r="B26" s="9">
+        <v>46264</v>
+      </c>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
+      <c r="E26" s="5" t="s">
+        <v>157</v>
+      </c>
       <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
+      <c r="G26" s="5">
+        <v>150</v>
+      </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
       <c r="J26" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>12205</v>
       </c>
       <c r="K26" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5939,18 +6139,26 @@
       <c r="N26" s="5"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="5"/>
-      <c r="B27" s="9"/>
+      <c r="A27" s="5">
+        <v>145</v>
+      </c>
+      <c r="B27" s="9">
+        <v>46264</v>
+      </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
+      <c r="E27" s="5" t="s">
+        <v>166</v>
+      </c>
       <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
+      <c r="G27" s="5">
+        <v>200</v>
+      </c>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>12005</v>
       </c>
       <c r="K27" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5961,18 +6169,26 @@
       <c r="N27" s="5"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="5"/>
-      <c r="B28" s="9"/>
+      <c r="A28" s="5">
+        <v>146</v>
+      </c>
+      <c r="B28" s="9">
+        <v>46264</v>
+      </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
+      <c r="E28" s="5" t="s">
+        <v>167</v>
+      </c>
       <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
+      <c r="G28" s="5">
+        <v>130</v>
+      </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>11875</v>
       </c>
       <c r="K28" s="5" t="str">
         <f t="shared" si="0"/>
@@ -5983,18 +6199,26 @@
       <c r="N28" s="5"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="5"/>
-      <c r="B29" s="9"/>
+      <c r="A29" s="5">
+        <v>147</v>
+      </c>
+      <c r="B29" s="9">
+        <v>46264</v>
+      </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
+      <c r="E29" s="5" t="s">
+        <v>168</v>
+      </c>
       <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
+      <c r="G29" s="5">
+        <v>50</v>
+      </c>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
       <c r="J29" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>11825</v>
       </c>
       <c r="K29" s="5" t="str">
         <f t="shared" si="0"/>
@@ -6005,18 +6229,26 @@
       <c r="N29" s="5"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="5"/>
-      <c r="B30" s="9"/>
+      <c r="A30" s="5">
+        <v>148</v>
+      </c>
+      <c r="B30" s="9">
+        <v>46265</v>
+      </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
+      <c r="E30" s="5" t="s">
+        <v>169</v>
+      </c>
       <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
+      <c r="G30" s="5">
+        <v>340</v>
+      </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="5">
         <f>J29-G30+H30</f>
-        <v>10876</v>
+        <v>11485</v>
       </c>
       <c r="K30" s="5" t="str">
         <f t="shared" si="0"/>
@@ -6027,18 +6259,26 @@
       <c r="N30" s="5"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="5"/>
-      <c r="B31" s="9"/>
+      <c r="A31" s="5">
+        <v>149</v>
+      </c>
+      <c r="B31" s="9">
+        <v>46265</v>
+      </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
-      <c r="E31" s="17"/>
+      <c r="E31" s="11" t="s">
+        <v>170</v>
+      </c>
       <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
+      <c r="G31" s="5">
+        <v>6000</v>
+      </c>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5">
         <f>J30-G31+H31</f>
-        <v>10876</v>
+        <v>5485</v>
       </c>
       <c r="K31" s="5" t="str">
         <f t="shared" si="0"/>
@@ -6049,18 +6289,26 @@
       <c r="N31" s="5"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="5"/>
-      <c r="B32" s="9"/>
+      <c r="A32" s="5">
+        <v>150</v>
+      </c>
+      <c r="B32" s="9">
+        <v>46265</v>
+      </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
+      <c r="E32" s="5" t="s">
+        <v>173</v>
+      </c>
       <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
+      <c r="G32" s="5">
+        <v>690</v>
+      </c>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>4795</v>
       </c>
       <c r="K32" s="5" t="str">
         <f t="shared" si="0"/>
@@ -6071,18 +6319,26 @@
       <c r="N32" s="5"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33" s="5"/>
-      <c r="B33" s="9"/>
+      <c r="A33" s="5">
+        <v>151</v>
+      </c>
+      <c r="B33" s="9">
+        <v>46265</v>
+      </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
+      <c r="E33" s="5" t="s">
+        <v>174</v>
+      </c>
       <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
+      <c r="G33" s="5">
+        <v>100</v>
+      </c>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>4695</v>
       </c>
       <c r="K33" s="5" t="str">
         <f t="shared" si="0"/>
@@ -6104,7 +6360,7 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5">
         <f t="shared" si="1"/>
-        <v>10876</v>
+        <v>4695</v>
       </c>
       <c r="K34" s="5" t="str">
         <f t="shared" si="0"/>
@@ -6125,11 +6381,11 @@
       <c r="F35" s="6"/>
       <c r="G35" s="6">
         <f>SUM(G4:G34)</f>
-        <v>381064</v>
+        <v>506640</v>
       </c>
       <c r="H35" s="6">
         <f>SUM(H4:H34)</f>
-        <v>391940</v>
+        <v>511335</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
